--- a/files/Cases/SodaVendingMachine/RQ3_SodaVendingMachine_perProduct_rawData.xlsx
+++ b/files/Cases/SodaVendingMachine/RQ3_SodaVendingMachine_perProduct_rawData.xlsx
@@ -1876,13 +1876,13 @@
         <v>26</v>
       </c>
       <c r="I24" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="J24" t="n">
-        <v>28.85</v>
+        <v>25</v>
       </c>
       <c r="K24" t="n">
-        <v>28.85</v>
+        <v>25</v>
       </c>
       <c r="L24" t="n">
         <v>8</v>
@@ -2296,13 +2296,13 @@
         <v>10</v>
       </c>
       <c r="I31" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J31" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="K31" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="L31" t="n">
         <v>5</v>
@@ -2356,13 +2356,13 @@
         <v>7</v>
       </c>
       <c r="I32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J32" t="n">
-        <v>57.14</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>57.14</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="L32" t="n">
         <v>5</v>
@@ -2716,13 +2716,13 @@
         <v>27</v>
       </c>
       <c r="I38" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="J38" t="n">
-        <v>27.78</v>
+        <v>16.67</v>
       </c>
       <c r="K38" t="n">
-        <v>27.78</v>
+        <v>16.67</v>
       </c>
       <c r="L38" t="n">
         <v>6</v>
@@ -2776,13 +2776,13 @@
         <v>25</v>
       </c>
       <c r="I39" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="J39" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="K39" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="L39" t="n">
         <v>6</v>
@@ -3676,13 +3676,13 @@
         <v>34</v>
       </c>
       <c r="I54" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="J54" t="n">
-        <v>30.88</v>
+        <v>35.29</v>
       </c>
       <c r="K54" t="n">
-        <v>30.88</v>
+        <v>35.29</v>
       </c>
       <c r="L54" t="n">
         <v>8</v>
@@ -3736,13 +3736,13 @@
         <v>32</v>
       </c>
       <c r="I55" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="J55" t="n">
-        <v>37.5</v>
+        <v>32.81</v>
       </c>
       <c r="K55" t="n">
-        <v>37.5</v>
+        <v>32.81</v>
       </c>
       <c r="L55" t="n">
         <v>8</v>
@@ -4387,25 +4387,25 @@
         <v>11</v>
       </c>
       <c r="F66" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G66" t="n">
-        <v>100</v>
+        <v>72.73</v>
       </c>
       <c r="H66" t="n">
         <v>18</v>
       </c>
       <c r="I66" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="J66" t="n">
-        <v>38.89</v>
+        <v>30.56</v>
       </c>
       <c r="K66" t="n">
         <v>38.89</v>
       </c>
       <c r="L66" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
@@ -4415,7 +4415,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>!f &gt;&gt; !f|3|3,!f &gt;&gt; c|1|1,!f &gt;&gt; s|1|1,!f &gt;&gt; t|1|1,c &gt;&gt; c|1|1,s &gt;&gt; !f|1|1,s &gt;&gt; s|1|1,t &gt;&gt; !f|1|1,t &gt;&gt; t|1|1</t>
+          <t>!f &gt;&gt; !f|3|3,!f &gt;&gt; c|1|1,!f &gt;&gt; s|1|1,!f &gt;&gt; t|0|1,c &gt;&gt; c|1|1,s &gt;&gt; !f|1|1,s &gt;&gt; s|1|1,t &gt;&gt; !f|0|1,t &gt;&gt; t|0|1</t>
         </is>
       </c>
       <c r="P66" t="n">
@@ -4636,13 +4636,13 @@
         <v>46</v>
       </c>
       <c r="I70" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J70" t="n">
-        <v>32.61</v>
+        <v>26.09</v>
       </c>
       <c r="K70" t="n">
-        <v>32.61</v>
+        <v>26.09</v>
       </c>
       <c r="L70" t="n">
         <v>11</v>
@@ -4867,25 +4867,25 @@
         <v>9</v>
       </c>
       <c r="F74" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G74" t="n">
-        <v>100</v>
+        <v>44.44</v>
       </c>
       <c r="H74" t="n">
         <v>14</v>
       </c>
       <c r="I74" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="J74" t="n">
-        <v>42.86</v>
+        <v>25</v>
       </c>
       <c r="K74" t="n">
-        <v>42.86</v>
+        <v>100</v>
       </c>
       <c r="L74" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
@@ -4895,7 +4895,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>!f &gt;&gt; !f|3|3,!f &gt;&gt; s|1|1,!f &gt;&gt; t|1|1,s &gt;&gt; !f|1|1,s &gt;&gt; s|1|1,t &gt;&gt; !f|1|1,t &gt;&gt; t|1|1</t>
+          <t>!f &gt;&gt; !f|1|3,!f &gt;&gt; s|0|1,!f &gt;&gt; t|1|1,s &gt;&gt; !f|0|1,s &gt;&gt; s|0|1,t &gt;&gt; !f|1|1,t &gt;&gt; t|1|1</t>
         </is>
       </c>
       <c r="P74" t="n">
@@ -5176,13 +5176,13 @@
         <v>43</v>
       </c>
       <c r="I79" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J79" t="n">
-        <v>18.6</v>
+        <v>25.58</v>
       </c>
       <c r="K79" t="n">
-        <v>18.6</v>
+        <v>25.58</v>
       </c>
       <c r="L79" t="n">
         <v>9</v>
@@ -5347,25 +5347,25 @@
         <v>6</v>
       </c>
       <c r="F82" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G82" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H82" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I82" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J82" t="n">
-        <v>62.5</v>
+        <v>33.33</v>
       </c>
       <c r="K82" t="n">
-        <v>62.5</v>
+        <v>72.22</v>
       </c>
       <c r="L82" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
@@ -5375,7 +5375,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>f &gt;&gt; s|1|1,f &gt;&gt; t|1|1,s &gt;&gt; f|1|1,s &gt;&gt; s|1|1,t &gt;&gt; f|1|1,t &gt;&gt; t|1|1</t>
+          <t>f &gt;&gt; s|0|1,f &gt;&gt; t|1|1,s &gt;&gt; f|0|1,s &gt;&gt; s|0|1,t &gt;&gt; f|1|1,t &gt;&gt; t|1|1</t>
         </is>
       </c>
       <c r="P82" t="n">
@@ -5827,25 +5827,25 @@
         <v>8</v>
       </c>
       <c r="F90" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G90" t="n">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="H90" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I90" t="n">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="J90" t="n">
-        <v>59.09</v>
+        <v>33.33</v>
       </c>
       <c r="K90" t="n">
-        <v>59.09</v>
+        <v>54.17</v>
       </c>
       <c r="L90" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M90" t="n">
         <v>0</v>
@@ -5855,7 +5855,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>c &gt;&gt; c|1|1,f &gt;&gt; c|1|1,f &gt;&gt; s|1|1,f &gt;&gt; t|1|1,s &gt;&gt; f|1|1,s &gt;&gt; s|1|1,t &gt;&gt; f|1|1,t &gt;&gt; t|1|1</t>
+          <t>c &gt;&gt; c|1|1,f &gt;&gt; c|1|1,f &gt;&gt; s|1|1,f &gt;&gt; t|0|1,s &gt;&gt; f|1|1,s &gt;&gt; s|1|1,t &gt;&gt; f|0|1,t &gt;&gt; t|0|1</t>
         </is>
       </c>
       <c r="P90" t="n">
@@ -7750,13 +7750,13 @@
         <v>26</v>
       </c>
       <c r="I24" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J24" t="n">
-        <v>26.92</v>
+        <v>19.23</v>
       </c>
       <c r="K24" t="n">
-        <v>26.92</v>
+        <v>19.23</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -8170,13 +8170,13 @@
         <v>10</v>
       </c>
       <c r="I31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J31" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="K31" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>7</v>
       </c>
       <c r="I32" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="J32" t="n">
-        <v>50</v>
+        <v>57.14</v>
       </c>
       <c r="K32" t="n">
-        <v>50</v>
+        <v>57.14</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -8590,13 +8590,13 @@
         <v>27</v>
       </c>
       <c r="I38" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J38" t="n">
-        <v>25.93</v>
+        <v>14.81</v>
       </c>
       <c r="K38" t="n">
-        <v>25.93</v>
+        <v>14.81</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -8650,13 +8650,13 @@
         <v>25</v>
       </c>
       <c r="I39" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J39" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="K39" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -10261,35 +10261,35 @@
         <v>11</v>
       </c>
       <c r="F66" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G66" t="n">
-        <v>100</v>
+        <v>90.91</v>
       </c>
       <c r="H66" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I66" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="J66" t="n">
-        <v>33.33</v>
+        <v>27.5</v>
       </c>
       <c r="K66" t="n">
-        <v>33.33</v>
+        <v>30</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N66" t="n">
         <v>4</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>!f|5|5,c|2|2,s|2|2,t|2|2</t>
+          <t>!f|5|5,c|2|2,s|2|2,t|1|2</t>
         </is>
       </c>
       <c r="P66" t="n">
@@ -10510,13 +10510,13 @@
         <v>46</v>
       </c>
       <c r="I70" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J70" t="n">
-        <v>30.43</v>
+        <v>17.39</v>
       </c>
       <c r="K70" t="n">
-        <v>30.43</v>
+        <v>17.39</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -11050,13 +11050,13 @@
         <v>43</v>
       </c>
       <c r="I79" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J79" t="n">
-        <v>11.63</v>
+        <v>18.6</v>
       </c>
       <c r="K79" t="n">
-        <v>11.63</v>
+        <v>18.6</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
@@ -11701,35 +11701,35 @@
         <v>8</v>
       </c>
       <c r="F90" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G90" t="n">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="H90" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I90" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J90" t="n">
-        <v>45.45</v>
+        <v>28.57</v>
       </c>
       <c r="K90" t="n">
-        <v>45.45</v>
+        <v>35.71</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N90" t="n">
         <v>4</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>c|2|2,f|2|2,s|2|2,t|2|2</t>
+          <t>c|2|2,f|2|2,s|2|2,t|1|2</t>
         </is>
       </c>
       <c r="P90" t="n">
